--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>22604.31</v>
+        <v>22767.28</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>78828</v>
+        <v>76983.95</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34154.59</v>
+        <v>35169.77</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41294.85</v>
+        <v>42043.55</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>64861.44</v>
+        <v>62793.22</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41573.79</v>
+        <v>42116.32</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>34079.44</v>
+        <v>33930.06</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>42037.07</v>
+        <v>42260.6</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41398.65</v>
+        <v>41618.79</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>41135.32</v>
+        <v>41723.93</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37925.49</v>
+        <v>37183.14</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>16182.26</v>
+        <v>15865.51</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34599.4</v>
+        <v>34429.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4357-535-CM25</t>
+          <t>1346283-66-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>22767.28</v>
+        <v>29558.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3281-75-CM25</t>
+          <t>1612-159-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42056.86</v>
+        <v>18521</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2322-1-CM26</t>
+          <t>4357-535-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>76983.95</v>
+        <v>22767.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>411-43-CM26</t>
+          <t>3281-75-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35169.77</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2381-302-CM26</t>
+          <t>2322-1-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42043.55</v>
+        <v>76983.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>411-142-CM26</t>
+          <t>411-43-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,33 +874,33 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>62793.22</v>
+        <v>35169.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2381-507-CM26</t>
+          <t>2381-302-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42116.32</v>
+        <v>42043.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2926-70-CM26</t>
+          <t>411-142-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>33930.06</v>
+        <v>62793.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>411-245-CM26</t>
+          <t>2381-507-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>42260.6</v>
+        <v>42116.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2924-31-CM26</t>
+          <t>2926-70-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41618.79</v>
+        <v>33930.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2381-645-CM26</t>
+          <t>411-245-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>41723.93</v>
+        <v>42260.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2322-454-CM26</t>
+          <t>2924-31-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37183.14</v>
+        <v>41618.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-455-CM26</t>
+          <t>2381-645-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>15865.51</v>
+        <v>41723.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1180885-32-CM26</t>
+          <t>2322-454-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,6 +1362,128 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
+        <v>37183.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2322-455-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>15865.51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1180885-32-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>34429.28</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1346283-66-CM25</t>
+          <t>3740-13-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29558.55</v>
+        <v>37402.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1612-159-CM25</t>
+          <t>3740-28-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18521</v>
+        <v>23876.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4357-535-CM25</t>
+          <t>3740-30-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>22767.28</v>
+        <v>27588.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3281-75-CM25</t>
+          <t>3740-32-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42056.86</v>
+        <v>33983.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2322-1-CM26</t>
+          <t>411-61-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>76983.95</v>
+        <v>33417.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>411-43-CM26</t>
+          <t>2381-154-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>35169.77</v>
+        <v>33513.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2381-302-CM26</t>
+          <t>3740-49-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42043.55</v>
+        <v>38959.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>411-142-CM26</t>
+          <t>2381-209-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>62793.22</v>
+        <v>35924.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2381-507-CM26</t>
+          <t>2322-170-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,28 +1057,28 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>42116.32</v>
+        <v>29359.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2926-70-CM26</t>
+          <t>1346283-66-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33930.06</v>
+        <v>29558.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>411-245-CM26</t>
+          <t>937-2-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>42260.6</v>
+        <v>35109.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2924-31-CM26</t>
+          <t>2381-485-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>41618.79</v>
+        <v>34603.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2381-645-CM26</t>
+          <t>411-8858-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>41723.93</v>
+        <v>32117.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2322-454-CM26</t>
+          <t>1612-159-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37183.14</v>
+        <v>18521</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2322-455-CM26</t>
+          <t>2924-17-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15865.51</v>
+        <v>19559.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1180885-32-CM26</t>
+          <t>707416-102-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,1109 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
+        <v>33239.42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>751-1436-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>29188.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2924-24-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>134069.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>651-232-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.815.000-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>29149.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4357-535-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.030.600-k</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>22767.28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3281-75-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>42056.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2322-1-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>76983.95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>411-43-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>35169.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2381-302-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>42043.55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>411-142-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>62793.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2381-507-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>42116.32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2926-70-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>33930.06</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>411-245-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>42260.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2924-31-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>41618.79</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2381-645-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>41723.93</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2322-454-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>37183.14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2322-455-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>15865.51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1180885-32-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>34429.28</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2381-984-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>39602.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2587,6 +2587,189 @@
       </c>
       <c r="M35" s="2" t="n">
         <v>39602.47</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2859-1011-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>71710.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>651-153-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.815.000-3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>29827.14</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>651-154-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.815.000-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>435.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1862,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1927,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2053,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2118,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2244,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2309,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2435,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2500,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2687,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2813,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2878,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/atacama.xlsx
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
